--- a/raw_data/2026-04-26_line-feed.xlsx
+++ b/raw_data/2026-04-26_line-feed.xlsx
@@ -382,8 +382,9 @@
       </c>
       <c r="C2" t="inlineStr">
         <is>
-          <t>a
-b</t>
+          <t>a 
+b 
+c</t>
         </is>
       </c>
     </row>
